--- a/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_5503_SW2.xlsx
+++ b/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_5503_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1667,6 +1667,308 @@
       <c r="AQ8" t="inlineStr">
         <is>
           <t>5503-20-20-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5503-24-24-FG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.92957</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.509</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.73909</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.73909</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.47867</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>5503-24-24-FG</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>45 deg Street Pipe Elbow, 1 1/2-11 1/2 NPTF (female) x 1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>5503</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: D@BORE, N3@DRIVE, N4@DRIVE, PORTDEPTH@BORE, W@HEX, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5503-24-24 (differs by -FG suffix) -&gt; dims NOT copied | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF end on the 45 deg leg (Q-NEW-ANGLEDHELIX): the library male end of the axis legs (ASME B1.20.3 cone + relief to the 5404 end length) turned to the 135 deg axis; its bore ends at the axis crossing as on every built root (Brennan 5501-08-08-FG / 5503-16-16-FG STEPs, OCP 2026-10-18: the male drill runs on a little past the crossing, and Brennan draws its own simplified thread cone and a bore-mouth countersink - NOT modelled); helical thread on the 45 deg leg (HelixThreadV, 2026-10-18): helix on the leg end face (circle centred on the leg axis), started in the Front Plane, right hand, into the part, tapered as on the axis legs; 60deg tooth profile on the Front Plane with its sides parallel / normal to the leg axis, swept along the helix - the thread of the axis legs (HelixThread) about the 135 deg axis; SolidWorks' Thread feature is not used there (an off-axis Thread feature crashed SolidWorks 2026-10-15); drawing-only thread, suppressed in the saved model and STEP; leg 1 port depth 0.940 = the row PORTDEPTH instead of MS51503 P1 1.16 (which does not fit the 1.69 leg): the port depth Brennan draws for -24: no Brennan STEP of this size; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: tap drill = the row's TAPDRILL (end library: the per-size tap drill every built female pipe port carries, Q-TRANSFER-ENDLIB = yes 2026-10-08), tapered helix over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - where that does not fit the short 45 deg leg (P1 &gt;= leg - 0.05) over the row's PORTDEPTH = the port depth Brennan draws for that size (Q-ANGLED-P1, settled from the Brennan STEPs 2026-10-18; said per leg below); connecting drill to the axis crossing = the tap drill carried to the crossing (Brennan 1504-06-06-FG / 5503-16-16-FG / 5505-08-08-FG STEPs, OCP 2026-10-18: the drill runs from the bottom of the tapered port to the axis crossing and ends flat there; the other leg bore opens into it); the 1.79deg port cone and the 45deg mouth chamfer are NOT modelled; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5503-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5503-24-24-FG (PARTcommunity / CADENAS, D@BORE=AD, N3@DRIVE=N1, N4@DRIVE=N, PORTDEPTH@BORE=BA, W@HEX=Y, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>5503-24-24-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5503-32-32-FG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.16957</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.812</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.812</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.81125</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.81125</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.62301</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>5503-32-32-FG</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>45 deg Street Pipe Elbow, 2-11 1/2 NPTF (female) x 2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>5503</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: D@BORE, N3@DRIVE, N4@DRIVE, PORTDEPTH@BORE, W@HEX, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5503-32-32 (differs by -FG suffix) -&gt; dims NOT copied | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF end on the 45 deg leg (Q-NEW-ANGLEDHELIX): the library male end of the axis legs (ASME B1.20.3 cone + relief to the 5404 end length) turned to the 135 deg axis; its bore ends at the axis crossing as on every built root (Brennan 5501-08-08-FG / 5503-16-16-FG STEPs, OCP 2026-10-18: the male drill runs on a little past the crossing, and Brennan draws its own simplified thread cone and a bore-mouth countersink - NOT modelled); helical thread on the 45 deg leg (HelixThreadV, 2026-10-18): helix on the leg end face (circle centred on the leg axis), started in the Front Plane, right hand, into the part, tapered as on the axis legs; 60deg tooth profile on the Front Plane with its sides parallel / normal to the leg axis, swept along the helix - the thread of the axis legs (HelixThread) about the 135 deg axis; SolidWorks' Thread feature is not used there (an off-axis Thread feature crashed SolidWorks 2026-10-15); drawing-only thread, suppressed in the saved model and STEP; leg 1 port depth 0.970 = the row PORTDEPTH instead of MS51503 P1 1.18 (which does not fit the 2.19 leg): the port depth Brennan draws for -32: 0.970 (Brennan 5406-40-32 STEP); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: tap drill = the row's TAPDRILL (end library: the per-size tap drill every built female pipe port carries, Q-TRANSFER-ENDLIB = yes 2026-10-08), tapered helix over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - where that does not fit the short 45 deg leg (P1 &gt;= leg - 0.05) over the row's PORTDEPTH = the port depth Brennan draws for that size (Q-ANGLED-P1, settled from the Brennan STEPs 2026-10-18; said per leg below); connecting drill to the axis crossing = the tap drill carried to the crossing (Brennan 1504-06-06-FG / 5503-16-16-FG / 5505-08-08-FG STEPs, OCP 2026-10-18: the drill runs from the bottom of the tapered port to the axis crossing and ends flat there; the other leg bore opens into it); the 1.79deg port cone and the 45deg mouth chamfer are NOT modelled; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5503-32-32 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5503-32-32-FG (PARTcommunity / CADENAS, D@BORE=AD, N3@DRIVE=N1, N4@DRIVE=N, PORTDEPTH@BORE=BA, W@HEX=Y, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>5503-32-32-FG</t>
         </is>
       </c>
     </row>
